--- a/assets/r02/sheets/空白NPC角色卡.xlsx
+++ b/assets/r02/sheets/空白NPC角色卡.xlsx
@@ -1,13 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NPC角色卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人物卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="參考資料" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC夥伴模板" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC夥伴模板1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC夥伴模板2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +30,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,11 +60,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00DCDCDC"/>
+        <bgColor rgb="00DCDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+        <bgColor rgb="008B0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -58,15 +79,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,29 +500,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NPC角色卡（空白模板）— 參照第4列範例填寫</t>
-        </is>
-      </c>
+          <t>SCP基金會 特工檔案</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>基本資料</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -464,127 +555,2384 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Lv</t>
+          <t>代號</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>子職業</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>許可等級</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>玩家</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>戰役</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>屬性（輸入區 → 自動計算派生值）</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STR 力量</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>AGI 敏捷</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>END 耐力</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>INT 智力</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PER 感知</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>WIL 意志</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>PRE 氣場</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>HIT</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>EVA</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SPD</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>武器</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>定位</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>陣營</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
+      <c r="B12" s="4">
+        <f>IF(OR(C4="",F9=""),"請填身份與END",F9+VLOOKUP(C4,參考資料!A:B,2,FALSE)+VLOOKUP(C4,參考資料!A:C,3,FALSE)*(IF(E4="",1,E4)-1))</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>IF(D10="","",MIN(99,50+D10))</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>INIT</t>
+        </is>
+      </c>
+      <c r="H12" s="4">
+        <f>IF(OR(D9="",B10=""),"",D9+B10+IFERROR(VLOOKUP(C4,參考資料!G:H,2,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MOV(m)</t>
+        </is>
+      </c>
+      <c r="J12" s="4">
+        <f>IF(OR(B9="",D9=""),"",(B9+D9)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>技能（24項）- 手動輸入</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>戰鬥</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>槍械(AGI)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>重武器(AGI)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>近戰(STR)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>投擲(AGI)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>迴避(AGI)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>技術</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>計算機(INT)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>工程(INT)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>爆破(INT)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>醫學(INT)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>密碼學(INT)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>駕駛(AGI)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>知識</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>異常學(INT)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>基金會史(INT)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>神秘學(INT)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>科學(INT)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>語言學(INT)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>社交</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>說服(PRE)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>欺騙(PRE)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>審訊(PRE)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>領導(PRE)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>生存</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>潛行(AGI)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>偵察(PER)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>生存(END)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>意志抵抗(WIL)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>資源池</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>狀態效果</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>當前</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>上限</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>恢復</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>恐慌</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>緊張</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>混亂</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>壓制</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>流血</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>身份能力 / 專長</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>能力名稱</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>裝備與武器</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>武器名稱</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>彈藥</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>護甲名稱</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>DR穿刺</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>DR切割</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>DR鈍擊</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>其他裝備 / 物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>背景 / 部門關係 / 道德追蹤</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>背景故事</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr"/>
+      <c r="B68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>部門關係(-10~+10)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>科學部</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>安保部</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>收容部</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>外勤部</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>資訊安保部</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>後勤部</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>倫理委員會</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr"/>
+      <c r="B70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>人性值(0-10)</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>道德值(0-10)</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="F35:J35"/>
+    <mergeCell ref="A66:J66"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>HP加值</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>每級HP</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>許可起點</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>核心屬性</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>MTF特遣隊員</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>MTF特遣隊員</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>外勤特工</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>外勤特工</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>桐人</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C4">
-        <f>20*8+96*2</f>
-        <v/>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F4">
-        <f>18*2+22</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>22*2</f>
-        <v/>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>闡釋者+逐闇者</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>二刀流</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>獨行</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>唯一技能二刀流</t>
-        </is>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>安保特工</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>安保特工</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>技術專家</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>技術專家</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>（角色圖：請貼入或註記圖片路徑）</t>
-        </is>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>醫療專員</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>醫療專員</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>研究員</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>研究員</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>D級人員</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>D級人員</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NPC夥伴模板（30秒建立 · 單人模式用）</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>基本資料</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>與PC關係</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>備註（性格/背景）</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>屬性（3項輸入 → 自動計算派生值）</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AGI 敏捷</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>END 耐力</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>WIL 意志</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STR 力量</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PER 感知</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PRE 氣場</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>IF(OR(C4="",D6=""),"",D6+VLOOKUP(C4,參考資料!A:B,2,FALSE)+VLOOKUP(C4,參考資料!A:C,3,FALSE)*(IF(D4="",1,D4)-1))</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MOV(m)</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>IF(OR(B6="",B7=""),"",(B7+B6)/2)</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>資源池</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>技能（填2項核心技能 + 1項弱項）</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>弱項</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>彈藥</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>DR穿刺</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>DR切割</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>行動規則（參考）</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>戰鬥：PC可用快速動作指令 → 夥伴在自己的先攻執行</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>核心技能可協助PC檢定（+10 TN）。弱項不可協助</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>夥伴無SAN/SP系統。HP=0 → 3輪內急救否則死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>信任度追蹤：−5（拒絕指令）/ +3（忠誠盟友）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>夥伴死亡不可復活。回站點後PRE+領導TN 0招募新夥伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>推薦組合見「單人規則補充」§1.3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NPC夥伴模板（30秒建立 · 單人模式用）</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>基本資料</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>與PC關係</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>備註（性格/背景）</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>屬性（3項輸入 → 自動計算派生值）</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AGI 敏捷</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>END 耐力</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>WIL 意志</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STR 力量</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PER 感知</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PRE 氣場</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>IF(OR(C4="",D6=""),"",D6+VLOOKUP(C4,參考資料!A:B,2,FALSE)+VLOOKUP(C4,參考資料!A:C,3,FALSE)*(IF(D4="",1,D4)-1))</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MOV(m)</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>IF(OR(B6="",B7=""),"",(B7+B6)/2)</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>資源池</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>技能（填2項核心技能 + 1項弱項）</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>弱項</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>彈藥</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>DR穿刺</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>DR切割</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>行動規則（參考）</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>戰鬥：PC可用快速動作指令 → 夥伴在自己的先攻執行</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>核心技能可協助PC檢定（+10 TN）。弱項不可協助</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>夥伴無SAN/SP系統。HP=0 → 3輪內急救否則死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>信任度追蹤：−5（拒絕指令）/ +3（忠誠盟友）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>夥伴死亡不可復活。回站點後PRE+領導TN 0招募新夥伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>推薦組合見「單人規則補充」§1.3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NPC夥伴模板（30秒建立 · 單人模式用）</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>基本資料</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>與PC關係</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>備註（性格/背景）</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>屬性（3項輸入 → 自動計算派生值）</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AGI 敏捷</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>END 耐力</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>WIL 意志</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STR 力量</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PER 感知</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PRE 氣場</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>IF(OR(C4="",D6=""),"",D6+VLOOKUP(C4,參考資料!A:B,2,FALSE)+VLOOKUP(C4,參考資料!A:C,3,FALSE)*(IF(D4="",1,D4)-1))</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MOV(m)</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>IF(OR(B6="",B7=""),"",(B7+B6)/2)</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>資源池</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>技能（填2項核心技能 + 1項弱項）</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>核心技能2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>弱項</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>彈藥</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>DR穿刺</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>DR切割</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>行動規則（參考）</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>戰鬥：PC可用快速動作指令 → 夥伴在自己的先攻執行</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>核心技能可協助PC檢定（+10 TN）。弱項不可協助</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>夥伴無SAN/SP系統。HP=0 → 3輪內急救否則死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>信任度追蹤：−5（拒絕指令）/ +3（忠誠盟友）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>夥伴死亡不可復活。回站點後PRE+領導TN 0招募新夥伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>推薦組合見「單人規則補充」§1.3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>